--- a/payment_forms/033_fitness_class_series_pre_order_form--payment_forms.xlsx
+++ b/payment_forms/033_fitness_class_series_pre_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Schedule Preferences</t>
+          <t>Schedule Preferences Schedule</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Participant Preferences</t>
+          <t>Participant Preferences Participant Preferences</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Confirm Session</t>
+          <t>Confirm Session Confirmation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -876,8 +876,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,12 +905,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'mon'}</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Mon'}</t>
+          <t>Mon</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'tue'}</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Tue'}</t>
+          <t>Tue</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'wed'}</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Wed'}</t>
+          <t>Wed</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'thu'}</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Thu'}</t>
+          <t>Thu</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'fri'}</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Fri'}</t>
+          <t>Fri</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'sat'}</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Sat'}</t>
+          <t>Sat</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'sun'}</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Sun'}</t>
+          <t>Sun</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Credit card'}</t>
+          <t>Credit card</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Bank transfer'}</t>
+          <t>Bank transfer</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'no_conflict'}</t>
+          <t>no_conflict</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'No conflict'}</t>
+          <t>No conflict</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'conflicted'}</t>
+          <t>conflicted</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Conflicted'}</t>
+          <t>Conflicted</t>
         </is>
       </c>
     </row>
